--- a/ui-testing/docs/Planilha de Controle de Testes - Sauce Demo.xlsx
+++ b/ui-testing/docs/Planilha de Controle de Testes - Sauce Demo.xlsx
@@ -848,7 +848,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> sou direcionado para a página página de produtos
+      <t xml:space="preserve"> sou direcionado para a página de produtos
 </t>
     </r>
   </si>
